--- a/output/remaining_area_and_pixels.xlsx
+++ b/output/remaining_area_and_pixels.xlsx
@@ -7,10 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Area Absolute" sheetId="1" r:id="rId1"/>
+    <sheet name="Area Relative" sheetId="2" r:id="rId2"/>
+    <sheet name="Pixels Absolute" sheetId="3" r:id="rId3"/>
+    <sheet name="Pixels Relative" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -375,7 +375,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -391,7 +391,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No mask</t>
         </is>
       </c>
     </row>
@@ -498,22 +498,22 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Broad (%)</t>
+          <t>Broad (ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Conifer (%)</t>
+          <t>Conifer (ha)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mixed (%)</t>
+          <t>Mixed (ha)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No mask</t>
         </is>
       </c>
     </row>
@@ -636,22 +636,22 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Broad (ncells)</t>
+          <t>Broad (ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Conifer (ncells)</t>
+          <t>Conifer (ha)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mixed (ncells)</t>
+          <t>Mixed (ha)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No mask</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Broad (ncells%)</t>
+          <t>Broad (ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Conifer (ncells%)</t>
+          <t>Conifer (ha)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mixed (ncells%)</t>
+          <t>Mixed (ha)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mask</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No mask</t>
         </is>
       </c>
     </row>

--- a/output/remaining_area_and_pixels.xlsx
+++ b/output/remaining_area_and_pixels.xlsx
@@ -375,7 +375,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
